--- a/data/trans_camb/P12_2_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P12_2_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 2,86</t>
+          <t>-3,97; 3,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 1,7</t>
+          <t>-5,02; 1,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 0,72</t>
+          <t>-8,11; 0,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,75; -0,66</t>
+          <t>-9,15; -0,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,67; -0,88</t>
+          <t>-10,16; -1,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 6,59</t>
+          <t>-5,86; 6,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 0,35</t>
+          <t>-5,44; 0,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,36; -0,09</t>
+          <t>-6,26; -0,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 1,46</t>
+          <t>-6,31; 1,46</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,92; 44,82</t>
+          <t>-39,24; 44,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-51,4; 24,48</t>
+          <t>-48,72; 25,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-80,92; 15,23</t>
+          <t>-84,3; 20,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-54,32; -3,86</t>
+          <t>-51,81; 0,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,92; -4,85</t>
+          <t>-55,24; -8,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,93; 46,33</t>
+          <t>-34,82; 47,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,64; 3,51</t>
+          <t>-41,16; 0,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 0,41</t>
+          <t>-47,17; -4,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-49,34; 15,01</t>
+          <t>-48,25; 14,29</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 0,53</t>
+          <t>-5,78; 0,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 0,28</t>
+          <t>-6,66; -0,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 2,46</t>
+          <t>-6,8; 2,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 0,7</t>
+          <t>-7,73; 0,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,65; -3,56</t>
+          <t>-11,7; -3,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,18; -2,91</t>
+          <t>-12,93; -2,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,59; -0,07</t>
+          <t>-5,83; -0,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,92; -2,53</t>
+          <t>-7,85; -2,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,07; -1,49</t>
+          <t>-8,22; -1,61</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,34; 5,46</t>
+          <t>-41,82; 9,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,7; 3,4</t>
+          <t>-48,44; 0,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,88; 21,05</t>
+          <t>-51,06; 21,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,02; 4,32</t>
+          <t>-37,7; 4,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,23; -21,6</t>
+          <t>-56,47; -20,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,2; -17,7</t>
+          <t>-63,75; -17,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,57; -0,39</t>
+          <t>-35,08; -2,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,04; -18,25</t>
+          <t>-47,84; -17,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-51,18; -10,79</t>
+          <t>-50,44; -11,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 1,71</t>
+          <t>-6,68; 1,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,86; -3,72</t>
+          <t>-11,33; -3,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 1,3</t>
+          <t>-7,57; 0,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 2,21</t>
+          <t>-6,87; 1,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,73; -3,5</t>
+          <t>-11,3; -3,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,99; -2,96</t>
+          <t>-11,04; -3,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 0,49</t>
+          <t>-5,59; 0,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,56; -4,98</t>
+          <t>-10,69; -4,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,88; -2,03</t>
+          <t>-8,09; -2,1</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 12,39</t>
+          <t>-35,41; 8,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,45; -25,45</t>
+          <t>-59,14; -25,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,79; 8,99</t>
+          <t>-38,17; 6,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,8; 11,03</t>
+          <t>-28,14; 10,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,4; -18,36</t>
+          <t>-48,53; -16,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,74; -14,96</t>
+          <t>-45,9; -16,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,15; 2,33</t>
+          <t>-26,15; 3,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,3; -27,68</t>
+          <t>-50,85; -27,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-38,52; -11,2</t>
+          <t>-38,43; -12,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 3,4</t>
+          <t>-5,8; 3,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 2,3</t>
+          <t>-6,5; 2,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 0,86</t>
+          <t>-14,06; 0,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 4,14</t>
+          <t>-7,29; 3,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,4; -3,55</t>
+          <t>-13,86; -3,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,39; -3,43</t>
+          <t>-13,25; -2,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 2,3</t>
+          <t>-4,81; 2,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,58; -1,98</t>
+          <t>-8,5; -1,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,59; -3,12</t>
+          <t>-13,8; -2,93</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,96; 23,75</t>
+          <t>-29,25; 20,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 16,09</t>
+          <t>-32,59; 14,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,55; 4,9</t>
+          <t>-71,6; 3,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-22,61; 16,94</t>
+          <t>-23,51; 15,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,2; -14,41</t>
+          <t>-44,03; -14,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,92; -13,4</t>
+          <t>-41,75; -11,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 10,91</t>
+          <t>-19,91; 10,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,86; -9,23</t>
+          <t>-34,55; -9,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-60,38; -14,84</t>
+          <t>-57,03; -13,37</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 1,31</t>
+          <t>-11,75; 1,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,2; -3,55</t>
+          <t>-15,44; -4,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,98; -2,82</t>
+          <t>-13,2; -2,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 3,58</t>
+          <t>-9,82; 3,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,04; -1,05</t>
+          <t>-14,1; -1,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,99; -2,56</t>
+          <t>-13,73; -2,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 0,21</t>
+          <t>-8,73; 0,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,1; -4,2</t>
+          <t>-13,34; -4,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,8; -4,18</t>
+          <t>-11,93; -4,03</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-36,17; 5,22</t>
+          <t>-36,31; 4,7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,06; -13,25</t>
+          <t>-48,38; -15,35</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-42,31; -9,97</t>
+          <t>-41,74; -9,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 10,87</t>
+          <t>-24,85; 9,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-35,49; -3,05</t>
+          <t>-35,96; -4,78</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-34,27; -7,66</t>
+          <t>-34,2; -8,13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 0,83</t>
+          <t>-25,15; 1,92</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-37,65; -13,59</t>
+          <t>-37,53; -13,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-33,31; -14,07</t>
+          <t>-34,17; -13,75</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 2,45</t>
+          <t>-11,87; 3,68</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 1,27</t>
+          <t>-13,26; 1,07</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,57; -3,66</t>
+          <t>-16,39; -3,49</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-23,57; -8,74</t>
+          <t>-23,2; -8,79</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-23,94; -9,63</t>
+          <t>-24,48; -10,06</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-47,71; -19,62</t>
+          <t>-48,64; -19,95</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-17,03; -5,61</t>
+          <t>-16,25; -5,57</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-17,55; -7,66</t>
+          <t>-17,82; -7,07</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-35,03; -14,95</t>
+          <t>-33,87; -15,03</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 9,15</t>
+          <t>-32,47; 12,91</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-36,98; 4,67</t>
+          <t>-36,43; 3,26</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-44,07; -12,4</t>
+          <t>-44,11; -12,23</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-41,96; -17,2</t>
+          <t>-41,8; -17,92</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-42,86; -19,67</t>
+          <t>-43,09; -20,35</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-83,39; -37,96</t>
+          <t>-83,81; -38,2</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-35,97; -13,16</t>
+          <t>-35,79; -13,51</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-38,0; -18,52</t>
+          <t>-38,05; -16,88</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-73,34; -34,74</t>
+          <t>-73,84; -34,68</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 4,88</t>
+          <t>-15,0; 4,55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 2,47</t>
+          <t>-14,79; 2,76</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-19,32; -3,4</t>
+          <t>-19,8; -2,76</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-15,99; -0,49</t>
+          <t>-16,17; -0,82</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-18,29; -1,36</t>
+          <t>-18,08; -2,06</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-21,17; -8,31</t>
+          <t>-21,1; -8,12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-13,71; -1,56</t>
+          <t>-13,21; -1,08</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-14,9; -2,47</t>
+          <t>-14,96; -2,82</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-18,54; -8,22</t>
+          <t>-18,59; -8,12</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 11,28</t>
+          <t>-28,7; 10,88</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-28,27; 5,61</t>
+          <t>-28,3; 6,7</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-36,58; -8,04</t>
+          <t>-37,46; -5,52</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-26,0; -0,82</t>
+          <t>-27,02; -1,6</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-29,86; -2,94</t>
+          <t>-29,59; -3,88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-34,42; -15,79</t>
+          <t>-34,98; -15,91</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-23,96; -3,01</t>
+          <t>-23,48; -2,19</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-26,25; -4,8</t>
+          <t>-26,67; -5,59</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-32,75; -16,39</t>
+          <t>-32,7; -16,33</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -0,38</t>
+          <t>-4,04; -0,2</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,66; -1,84</t>
+          <t>-5,67; -2,05</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,47; -1,68</t>
+          <t>-7,08; -1,59</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,37; -2,09</t>
+          <t>-6,44; -2,09</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-9,6; -5,27</t>
+          <t>-9,75; -5,35</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-12,64; -5,64</t>
+          <t>-12,25; -5,71</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,64; -1,68</t>
+          <t>-4,66; -1,7</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,96; -4,05</t>
+          <t>-7,15; -4,23</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-8,51; -4,11</t>
+          <t>-8,26; -3,95</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-20,43; -2,06</t>
+          <t>-20,0; -1,33</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-27,63; -9,85</t>
+          <t>-27,6; -11,07</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-36,83; -8,84</t>
+          <t>-36,18; -8,34</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-20,78; -7,32</t>
+          <t>-20,95; -7,27</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-31,2; -18,31</t>
+          <t>-31,61; -18,72</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-42,08; -19,56</t>
+          <t>-40,38; -19,91</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-18,15; -6,93</t>
+          <t>-18,28; -7,1</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-27,67; -16,88</t>
+          <t>-28,02; -17,69</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-33,82; -17,27</t>
+          <t>-33,13; -16,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P12_2_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P12_2_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-4,2</t>
+          <t>-4,11</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,7</t>
+          <t>-2,07</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 3,04</t>
+          <t>-3,75; 2,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 1,79</t>
+          <t>-5,62; 1,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 0,7</t>
+          <t>-7,84; 0,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,15; -0,05</t>
+          <t>-9,38; -0,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,16; -1,28</t>
+          <t>-9,66; -0,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 6,53</t>
+          <t>-5,82; 7,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 0,04</t>
+          <t>-5,56; 0,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,26; -0,63</t>
+          <t>-6,04; -0,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 1,46</t>
+          <t>-5,59; 2,14</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-49,83%</t>
+          <t>-48,76%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-0,04%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-22,82%</t>
+          <t>-17,48%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,24; 44,91</t>
+          <t>-37,39; 43,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-48,72; 25,76</t>
+          <t>-52,05; 28,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-84,3; 20,29</t>
+          <t>-78,55; 9,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,81; 0,21</t>
+          <t>-53,1; 0,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,24; -8,33</t>
+          <t>-54,96; -5,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 47,01</t>
+          <t>-33,63; 53,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,16; 0,58</t>
+          <t>-42,21; 4,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,17; -4,88</t>
+          <t>-45,83; -5,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-48,25; 14,29</t>
+          <t>-44,89; 19,09</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,65</t>
+          <t>-1,32</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-7,49</t>
+          <t>-5,12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,74</t>
+          <t>-2,93</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 0,78</t>
+          <t>-6,01; 0,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,66; -0,03</t>
+          <t>-6,77; 0,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 2,15</t>
+          <t>-5,08; 3,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 0,69</t>
+          <t>-7,86; 0,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,7; -3,6</t>
+          <t>-11,69; -3,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,93; -2,89</t>
+          <t>-9,32; -0,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,83; -0,33</t>
+          <t>-6,06; -0,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,85; -2,56</t>
+          <t>-7,79; -2,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,22; -1,61</t>
+          <t>-6,31; 0,17</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-21,98%</t>
+          <t>-10,97%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-40,67%</t>
+          <t>-27,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-31,65%</t>
+          <t>-19,56%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,82; 9,2</t>
+          <t>-43,31; 10,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,44; 0,93</t>
+          <t>-48,73; 2,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,06; 21,31</t>
+          <t>-37,69; 34,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,7; 4,38</t>
+          <t>-37,6; 4,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,47; -20,57</t>
+          <t>-56,58; -20,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,75; -17,4</t>
+          <t>-46,05; -1,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,08; -2,24</t>
+          <t>-35,73; -2,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,84; -17,92</t>
+          <t>-47,93; -16,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-50,44; -11,02</t>
+          <t>-38,29; 1,27</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,0</t>
+          <t>-3,95</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-7,1</t>
+          <t>-6,33</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-5,14</t>
+          <t>-5,23</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 1,37</t>
+          <t>-6,57; 1,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,33; -3,98</t>
+          <t>-11,25; -3,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 0,94</t>
+          <t>-8,41; -0,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 1,99</t>
+          <t>-6,27; 2,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,3; -3,16</t>
+          <t>-11,81; -3,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,04; -3,16</t>
+          <t>-10,42; -2,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 0,52</t>
+          <t>-5,54; 0,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,69; -4,99</t>
+          <t>-10,36; -4,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,09; -2,1</t>
+          <t>-8,19; -2,56</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-17,53%</t>
+          <t>-23,09%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-32,49%</t>
+          <t>-28,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-26,26%</t>
+          <t>-26,73%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 8,83</t>
+          <t>-34,01; 8,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-59,14; -25,63</t>
+          <t>-58,43; -24,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,17; 6,76</t>
+          <t>-42,92; -0,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 10,26</t>
+          <t>-26,45; 11,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,53; -16,97</t>
+          <t>-48,65; -18,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,9; -16,12</t>
+          <t>-42,58; -13,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,15; 3,49</t>
+          <t>-25,95; 4,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,85; -27,9</t>
+          <t>-49,21; -25,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-38,43; -12,03</t>
+          <t>-38,36; -13,99</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-5,63</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,0</t>
+          <t>-7,44</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-7,25</t>
+          <t>-4,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 3,2</t>
+          <t>-6,65; 3,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 2,46</t>
+          <t>-7,53; 2,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 0,65</t>
+          <t>-6,17; 2,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 3,95</t>
+          <t>-7,43; 3,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,86; -3,66</t>
+          <t>-13,19; -3,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,25; -2,89</t>
+          <t>-12,12; -3,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 2,34</t>
+          <t>-5,16; 2,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,5; -1,95</t>
+          <t>-8,89; -1,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,8; -2,93</t>
+          <t>-7,41; -1,08</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-31,97%</t>
+          <t>-6,02%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-28,3%</t>
+          <t>-26,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-31,63%</t>
+          <t>-18,23%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-29,25; 20,16</t>
+          <t>-31,59; 22,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-32,59; 14,53</t>
+          <t>-33,82; 15,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-71,6; 3,85</t>
+          <t>-29,88; 19,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,51; 15,44</t>
+          <t>-23,73; 14,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,03; -14,52</t>
+          <t>-43,15; -12,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,75; -11,61</t>
+          <t>-38,09; -11,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,91; 10,85</t>
+          <t>-20,72; 9,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,55; -9,49</t>
+          <t>-35,55; -7,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-57,03; -13,37</t>
+          <t>-29,34; -4,97</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-7,89</t>
+          <t>-8,13</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-8,2</t>
+          <t>-8,1</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-8,16</t>
+          <t>-8,19</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 1,1</t>
+          <t>-11,43; 0,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,44; -4,13</t>
+          <t>-15,63; -3,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,2; -2,07</t>
+          <t>-13,44; -2,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 3,05</t>
+          <t>-9,87; 3,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,1; -1,58</t>
+          <t>-13,79; -1,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,73; -2,75</t>
+          <t>-14,45; -3,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 0,58</t>
+          <t>-9,04; 0,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,34; -4,19</t>
+          <t>-12,87; -4,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,93; -4,03</t>
+          <t>-11,83; -4,43</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-27,15%</t>
+          <t>-27,98%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-22,71%</t>
+          <t>-22,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-25,0%</t>
+          <t>-25,1%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-36,31; 4,7</t>
+          <t>-36,3; 2,96</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,38; -15,35</t>
+          <t>-48,44; -14,66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-41,74; -9,03</t>
+          <t>-41,47; -8,89</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 9,72</t>
+          <t>-25,0; 9,57</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-35,96; -4,78</t>
+          <t>-34,98; -3,39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-34,2; -8,13</t>
+          <t>-35,3; -9,45</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-25,15; 1,92</t>
+          <t>-25,55; 0,56</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-37,53; -13,87</t>
+          <t>-36,64; -13,38</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-34,17; -13,75</t>
+          <t>-33,6; -14,97</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-9,82</t>
+          <t>-10,86</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-32,26</t>
+          <t>-21,56</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-22,12</t>
+          <t>-16,84</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 3,68</t>
+          <t>-12,07; 2,77</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 1,07</t>
+          <t>-13,26; 1,02</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-16,39; -3,49</t>
+          <t>-16,93; -5,32</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-23,2; -8,79</t>
+          <t>-23,47; -9,76</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-24,48; -10,06</t>
+          <t>-25,16; -10,6</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-48,64; -19,95</t>
+          <t>-27,69; -15,11</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-16,25; -5,57</t>
+          <t>-17,06; -6,17</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-17,82; -7,07</t>
+          <t>-16,95; -7,0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-33,87; -15,03</t>
+          <t>-21,85; -12,75</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-29,71%</t>
+          <t>-32,87%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-60,61%</t>
+          <t>-40,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-50,34%</t>
+          <t>-38,32%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 12,91</t>
+          <t>-32,72; 11,75</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-36,43; 3,26</t>
+          <t>-36,58; 3,17</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-44,11; -12,23</t>
+          <t>-45,48; -18,22</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-41,8; -17,92</t>
+          <t>-41,33; -18,92</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-43,09; -20,35</t>
+          <t>-43,59; -20,64</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-83,81; -38,2</t>
+          <t>-48,67; -31,01</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-35,79; -13,51</t>
+          <t>-36,59; -14,75</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-38,05; -16,88</t>
+          <t>-36,9; -17,39</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-73,84; -34,68</t>
+          <t>-46,31; -30,71</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-11,17</t>
+          <t>-11,12</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-15,01</t>
+          <t>-15,24</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-13,61</t>
+          <t>-13,73</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 4,55</t>
+          <t>-15,91; 3,57</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 2,76</t>
+          <t>-14,42; 3,53</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-19,8; -2,76</t>
+          <t>-18,89; -3,13</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-16,17; -0,82</t>
+          <t>-16,5; -0,4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-18,08; -2,06</t>
+          <t>-17,37; -1,7</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-21,1; -8,12</t>
+          <t>-22,06; -8,09</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-13,21; -1,08</t>
+          <t>-13,21; -1,06</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-14,96; -2,82</t>
+          <t>-14,12; -2,07</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-18,59; -8,12</t>
+          <t>-18,57; -8,55</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-23,62%</t>
+          <t>-23,52%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-26,36%</t>
+          <t>-26,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-25,57%</t>
+          <t>-25,8%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 10,88</t>
+          <t>-29,88; 8,42</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 6,7</t>
+          <t>-27,34; 8,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,46; -5,52</t>
+          <t>-35,53; -6,02</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-27,02; -1,6</t>
+          <t>-27,09; -0,92</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-29,59; -3,88</t>
+          <t>-28,78; -3,49</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-34,98; -15,91</t>
+          <t>-35,6; -15,66</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-23,48; -2,19</t>
+          <t>-23,27; -2,03</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-26,67; -5,59</t>
+          <t>-25,02; -4,4</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-32,7; -16,33</t>
+          <t>-32,79; -17,07</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-3,75</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-8,16</t>
+          <t>-6,17</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-5,95</t>
+          <t>-4,39</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,04; -0,2</t>
+          <t>-4,08; -0,29</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,67; -2,05</t>
+          <t>-5,49; -2,1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -1,59</t>
+          <t>-4,47; -0,8</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,44; -2,09</t>
+          <t>-6,3; -1,83</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-9,75; -5,35</t>
+          <t>-9,5; -5,23</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-12,25; -5,71</t>
+          <t>-8,29; -4,28</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,66; -1,7</t>
+          <t>-4,82; -1,8</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,15; -4,23</t>
+          <t>-7,12; -4,09</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-8,26; -3,95</t>
+          <t>-5,77; -3,06</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-19,23%</t>
+          <t>-13,47%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-27,5%</t>
+          <t>-20,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-24,13%</t>
+          <t>-17,78%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-20,0; -1,33</t>
+          <t>-20,14; -1,63</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-27,6; -11,07</t>
+          <t>-27,15; -11,27</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-36,18; -8,34</t>
+          <t>-21,9; -4,27</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-20,95; -7,27</t>
+          <t>-20,44; -6,43</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-31,61; -18,72</t>
+          <t>-31,14; -18,4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-40,38; -19,91</t>
+          <t>-26,83; -15,13</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-18,28; -7,1</t>
+          <t>-18,88; -7,51</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-28,02; -17,69</t>
+          <t>-27,94; -17,02</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-33,13; -16,58</t>
+          <t>-22,62; -12,89</t>
         </is>
       </c>
     </row>
